--- a/data/trans_orig/IP07A15-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A15-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que los padres tubiesen suficiente tiempo par él/ella en 2007 (tasa de respuesta: 98,9%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2007 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20557</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31752</t>
+          <t>32271</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18610</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29897</t>
+          <t>29619</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42963</t>
+          <t>42141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58514</t>
+          <t>57973</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,21%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14555</t>
+          <t>14335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25696</t>
+          <t>25249</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13273</t>
+          <t>13537</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24040</t>
+          <t>23890</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30592</t>
+          <t>30932</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>46786</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13242</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95275</t>
+          <t>95057</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117861</t>
+          <t>118516</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99311</t>
+          <t>99350</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123784</t>
+          <t>124240</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202556</t>
+          <t>201302</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>235306</t>
+          <t>235320</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67526</t>
+          <t>67312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89150</t>
+          <t>89504</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86485</t>
+          <t>84631</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109109</t>
+          <t>109246</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158421</t>
+          <t>159586</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192190</t>
+          <t>192501</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9916</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22237</t>
+          <t>21971</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17613</t>
+          <t>18301</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32953</t>
+          <t>33262</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31120</t>
+          <t>31332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50122</t>
+          <t>50588</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18349</t>
+          <t>18016</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30040</t>
+          <t>29992</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21504</t>
+          <t>21748</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33929</t>
+          <t>34014</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42650</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61311</t>
+          <t>60536</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,13%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24819</t>
+          <t>24483</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37740</t>
+          <t>37098</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>17599</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30474</t>
+          <t>29636</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44822</t>
+          <t>45659</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63765</t>
+          <t>63483</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17058</t>
+          <t>17122</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>12446</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12630</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26135</t>
+          <t>26516</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>145050</t>
+          <t>143320</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>173446</t>
+          <t>172100</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>149774</t>
+          <t>149671</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>178783</t>
+          <t>177654</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>303180</t>
+          <t>298946</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>343844</t>
+          <t>341740</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,64%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113783</t>
+          <t>114229</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>141400</t>
+          <t>142264</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>123378</t>
+          <t>123813</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>154051</t>
+          <t>153391</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>245882</t>
+          <t>247523</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>286418</t>
+          <t>288973</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23018</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40202</t>
+          <t>39451</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>28287</t>
+          <t>27856</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47558</t>
+          <t>47264</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>54807</t>
+          <t>54271</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>81958</t>
+          <t>78720</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que los padres tubiesen suficiente tiempo par él/ella en 2012 (tasa de respuesta: 97,71%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2012 (tasa de respuesta: 97,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27938</t>
+          <t>27953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39699</t>
+          <t>39540</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16351</t>
+          <t>16395</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27847</t>
+          <t>27550</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47753</t>
+          <t>48020</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64219</t>
+          <t>64506</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18886</t>
+          <t>19053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11162</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>22255</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>22302</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37116</t>
+          <t>37751</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>38,16%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11067</t>
+          <t>10709</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>12190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19435</t>
+          <t>19186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99078</t>
+          <t>99859</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123151</t>
+          <t>121467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>115795</t>
+          <t>116416</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139919</t>
+          <t>139560</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221519</t>
+          <t>219442</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256382</t>
+          <t>254335</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>58,98%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59192</t>
+          <t>59161</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81716</t>
+          <t>80720</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68100</t>
+          <t>67508</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90754</t>
+          <t>90834</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133080</t>
+          <t>132549</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>165107</t>
+          <t>164720</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>15638</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30029</t>
+          <t>30045</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25109</t>
+          <t>25787</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31277</t>
+          <t>31254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51282</t>
+          <t>51775</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>610</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7389</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23833</t>
+          <t>23463</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37472</t>
+          <t>37480</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20576</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33146</t>
+          <t>32522</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49442</t>
+          <t>47501</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67020</t>
+          <t>65013</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>53,57%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20917</t>
+          <t>21162</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34431</t>
+          <t>34700</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19827</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32447</t>
+          <t>32477</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44113</t>
+          <t>45364</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62794</t>
+          <t>62915</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,85%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14589</t>
+          <t>14549</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>160192</t>
+          <t>158662</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>190536</t>
+          <t>189005</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>161342</t>
+          <t>161523</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>190949</t>
+          <t>190825</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>333256</t>
+          <t>332480</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>373581</t>
+          <t>373666</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95769</t>
+          <t>97487</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124692</t>
+          <t>124981</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>107400</t>
+          <t>108297</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>137014</t>
+          <t>137129</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>212155</t>
+          <t>212380</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>252264</t>
+          <t>251701</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,63%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25049</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44483</t>
+          <t>42902</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>38177</t>
+          <t>37770</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>50336</t>
+          <t>50029</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>74767</t>
+          <t>75043</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que los padres tubiesen suficiente tiempo par él/ella en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19352</t>
+          <t>19849</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>10816</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20723</t>
+          <t>20274</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23386</t>
+          <t>23634</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37105</t>
+          <t>37309</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18659</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>11675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>21692</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24553</t>
+          <t>23800</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>37367</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,59%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10098</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>125676</t>
+          <t>125145</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>151630</t>
+          <t>151992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124331</t>
+          <t>124328</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150339</t>
+          <t>150742</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>256660</t>
+          <t>256056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292056</t>
+          <t>294908</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,82%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76632</t>
+          <t>77624</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101505</t>
+          <t>102993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72409</t>
+          <t>73768</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97982</t>
+          <t>98763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159921</t>
+          <t>158382</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>193238</t>
+          <t>193582</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12801</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26466</t>
+          <t>26372</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11389</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25222</t>
+          <t>24661</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26889</t>
+          <t>27281</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47990</t>
+          <t>46595</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>714</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12097</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31318</t>
+          <t>31448</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46267</t>
+          <t>45858</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34412</t>
+          <t>34140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49097</t>
+          <t>49033</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70431</t>
+          <t>70311</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90951</t>
+          <t>91140</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18038</t>
+          <t>18771</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31751</t>
+          <t>32202</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24169</t>
+          <t>24256</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38618</t>
+          <t>39045</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47186</t>
+          <t>46236</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66422</t>
+          <t>66283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>15839</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1763</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9491</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21319</t>
+          <t>22202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>177106</t>
+          <t>175656</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>207296</t>
+          <t>207277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>180144</t>
+          <t>179935</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>210791</t>
+          <t>209968</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>365682</t>
+          <t>364597</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>408658</t>
+          <t>408245</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,18%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>114167</t>
+          <t>112328</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>143451</t>
+          <t>143418</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>118516</t>
+          <t>119256</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>148567</t>
+          <t>149030</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>241959</t>
+          <t>240870</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>282592</t>
+          <t>283003</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22740</t>
+          <t>22816</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41149</t>
+          <t>40988</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>18012</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>34353</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>44993</t>
+          <t>45085</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>68704</t>
+          <t>68805</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15020</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A15-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A15-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2007 (tasa de respuesta: 98,9%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24047</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18618</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29611</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,92%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>39,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>26653</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20802</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>32271</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20714</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>32192</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>52,6%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>41,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>63,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>24047</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>18950</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>29619</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>50,92%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42141</t>
+          <t>42111</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57973</t>
+          <t>58079</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18560</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13462</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24155</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>39,3%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>51,14%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>19440</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14335</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25249</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14369</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25483</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,36%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,29%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>49,83%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18560</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13537</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23890</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>39,3%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30932</t>
+          <t>30782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46786</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,0%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3943</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1907</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7868</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4581</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1945</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8896</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8851</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>9,04%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3943</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1360</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7753</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>14060</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -1061,107 +1061,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3806</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,06%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>680</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4305</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3411</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,11%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>111748</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>99363</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>123185</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>47,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>42,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>52,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>107378</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>95057</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>118516</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>95984</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>120081</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>52,98%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>58,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>111748</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>99350</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>124240</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>47,48%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>201302</t>
+          <t>202887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>235320</t>
+          <t>235685</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,81%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>97623</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>86252</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>109495</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>36,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>77478</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67312</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>89504</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>67599</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>89594</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,23%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>97623</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>84631</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>109246</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>41,48%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159586</t>
+          <t>158569</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192501</t>
+          <t>192197</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>24670</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17190</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32360</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13,75%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>15317</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10309</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>21971</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10348</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>22365</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>7,56%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,84%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>24670</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>18301</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>33262</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31332</t>
+          <t>30820</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50588</t>
+          <t>50251</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -1743,74 +1743,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4117</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1960</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>5263</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3948</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -1861,102 +1861,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3187</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>537</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2696</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3141</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3190</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3815</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1171</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3997</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>235360</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>235360</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>235360</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>202670</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>202670</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>202670</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>235360</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>235360</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>235360</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>27892</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>21466</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>34201</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>46,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>35,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>57,17%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>24144</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18016</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>29992</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18155</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>31008</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>36,6%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>27,31%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>45,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>27892</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>21748</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>34014</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>46,63%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>42988</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60536</t>
+          <t>60728</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23424</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17374</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>30273</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>39,16%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>29,04%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>50,61%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>30837</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>24483</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>37098</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>24087</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>46,75%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>37,12%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>56,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>23424</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>17599</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>29636</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>39,16%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45659</t>
+          <t>45219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63483</t>
+          <t>62906</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,01%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7702</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3869</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>12353</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,47%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>20,65%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>10984</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6764</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>17122</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>6910</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>17265</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>16,65%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>10,25%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>25,96%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7702</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>4451</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>12446</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>12,88%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12945</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26516</t>
+          <t>26212</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -2425,107 +2425,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6626</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>802</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3976</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3652</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4040</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59820</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59820</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59820</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>65965</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>65965</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>65965</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59820</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59820</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59820</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,107 +2768,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>163687</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>148513</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>177965</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>47,8%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>43,37%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>51,97%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>158176</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>143320</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>172100</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>144658</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>173228</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>49,54%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>44,88%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>53,9%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>163687</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>149671</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>177654</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>47,8%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>54,25%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>321863</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>301312</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>343329</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>48,64%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>45,53%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>51,88%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>321863</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>298946</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>341740</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>48,64%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>45,18%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>51,64%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>139608</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>125776</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>155540</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>40,77%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>36,73%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>127755</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>114229</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>142264</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>113532</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>141624</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>40,01%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>35,77%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>44,55%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>139608</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>123813</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>153391</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>40,77%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>247523</t>
+          <t>247983</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>288973</t>
+          <t>288109</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>36315</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>28440</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>46529</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>10,61%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>8,31%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>13,59%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>30881</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>22370</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>39451</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>22661</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>39760</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>9,67%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>36315</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>27856</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>47264</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>54271</t>
+          <t>55984</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>78720</t>
+          <t>80199</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -3112,67 +3112,67 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>2165</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6052</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>1960</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>5281</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5222</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2165</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5826</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8975</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -3225,102 +3225,102 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3179</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>537</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2861</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2567</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>4145</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1171</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>4114</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>342410</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>342410</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>342410</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>474</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>319309</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>319309</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>319309</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>342410</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>342410</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>342410</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2012 (tasa de respuesta: 97,71%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 97,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21993</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17089</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28068</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47,96%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>37,27%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>34192</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>27953</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>39540</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>28595</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>40212</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>64,41%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>52,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>21993</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>16395</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>27550</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>47,96%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48020</t>
+          <t>47892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64506</t>
+          <t>64269</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,96%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16526</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11520</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22320</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,12%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>48,68%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>12982</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8673</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19053</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8287</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>18654</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>24,46%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>35,89%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16526</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11162</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22255</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,04%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22302</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37751</t>
+          <t>37547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -3907,72 +3907,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6704</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2989</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11874</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14,62%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>25,9%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>5908</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2648</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2666</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10897</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>11,13%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,17%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>6704</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3163</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12190</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>14,62%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19186</t>
+          <t>19967</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -4020,107 +4020,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2879</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>630</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3740</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2803</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>128115</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>115949</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>140343</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>56,57%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>51,2%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>61,97%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>110594</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>99859</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>121467</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>99055</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>121887</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>54,01%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>48,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>59,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>128115</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>116416</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>139560</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>56,57%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>219442</t>
+          <t>222907</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>254335</t>
+          <t>256970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>78993</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67036</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>90335</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,89%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>69881</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>59161</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>80720</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>59121</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>81606</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>34,13%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28,89%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>78993</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>67508</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>90834</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>34,88%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132549</t>
+          <t>132645</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164720</t>
+          <t>165278</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>17968</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12592</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>25668</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,33%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22075</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>15638</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>30045</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>15755</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>29689</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>10,78%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>17968</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>12557</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>25787</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31254</t>
+          <t>30866</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51775</t>
+          <t>50153</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -4702,74 +4702,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3132</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2206</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6480</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2513</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -4815,107 +4815,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4443</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>767</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4091</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3850</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4164</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>226463</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>226463</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>226463</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>293</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>204757</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>204757</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>204757</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>226463</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>226463</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>226463</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26479</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>20544</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>32399</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>45,71%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>35,46%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>30513</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>23463</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>37480</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>23707</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>37559</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>48,11%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>37,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>59,1%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>26479</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>20436</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>32522</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>45,71%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47501</t>
+          <t>48138</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65013</t>
+          <t>66188</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>54,54%</t>
         </is>
       </c>
     </row>
@@ -5163,67 +5163,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>26150</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20088</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>32679</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>45,14%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>34,67%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>56,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>27755</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>21162</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>34700</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>20882</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>33907</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>43,77%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,37%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>54,72%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>26150</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>20063</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>32477</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>45,14%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45364</t>
+          <t>44594</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62915</t>
+          <t>62924</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5271,72 +5271,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3798</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7958</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>13,74%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>5150</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9598</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2173</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>10185</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>8,12%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>15,13%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3798</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1385</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7331</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14549</t>
+          <t>14273</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -5384,107 +5384,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5079</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1506</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5102</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5665</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1506</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5427</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>176586</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>161346</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>191546</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>53,47%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>48,86%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>58,0%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>175299</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>158662</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>189005</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>161330</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>190904</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>54,57%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>49,39%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>58,83%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>176586</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>161523</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>190825</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>53,47%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>332480</t>
+          <t>330765</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>373666</t>
+          <t>372783</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>121669</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>108197</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>137893</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>36,84%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>32,76%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>41,75%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>110619</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>97487</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>124981</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>96928</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>124177</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>34,43%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>30,35%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>38,9%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>121669</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>108297</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>137129</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>36,84%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>212380</t>
+          <t>211895</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>251701</t>
+          <t>252490</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>28471</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>21159</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>38004</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>11,51%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>33133</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>24994</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>42902</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>24287</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>42667</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>10,31%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>13,35%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>28471</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>20481</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>37770</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>50029</t>
+          <t>50554</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>75043</t>
+          <t>75573</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -6066,72 +6066,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2756</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7095</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>2206</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>611</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6048</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5989</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2756</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>6670</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -6179,92 +6179,92 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4640</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>767</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
         <is>
           <t>3832</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>3850</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>330248</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>330248</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>330248</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>321258</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>321258</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>321258</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>330248</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>330248</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>330248</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6645,67 +6645,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>15449</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10664</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20334</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>42,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>29,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>55,5%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>14875</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10410</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19849</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9901</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19335</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>46,76%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>15449</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10816</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>20274</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>42,17%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23634</t>
+          <t>23658</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37309</t>
+          <t>37470</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,74%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16828</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11569</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21643</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>45,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>31,58%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>59,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>14155</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9595</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18789</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9983</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19400</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>44,49%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>59,06%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16828</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11675</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21692</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>45,93%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>23870</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37367</t>
+          <t>37903</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>55,37%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3690</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7604</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10,07%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2078</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5366</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5518</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>6,53%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>1,96%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,87%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3690</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1313</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7591</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>10,07%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10780</t>
+          <t>10442</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -6984,102 +6984,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3283</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>706</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3538</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2922</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,22%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3452</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4750</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1377</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4770</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>137666</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>124956</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>150594</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>56,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>51,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>61,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>138013</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>125145</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>151992</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>124649</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>150851</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>55,41%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50,24%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>61,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>137666</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>124328</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>150742</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>56,43%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>256056</t>
+          <t>255584</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>294908</t>
+          <t>294013</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,63%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>85679</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>73973</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>98376</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35,12%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,33%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>89277</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>77624</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>102993</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>76832</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>102710</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>35,84%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>41,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>85679</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>73768</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>98763</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>35,12%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158382</t>
+          <t>157777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>193582</t>
+          <t>192537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,05%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>17416</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11415</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>25106</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,29%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>18432</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11944</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26372</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>12839</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>27420</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>7,4%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,59%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>17416</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>11038</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>24661</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27281</t>
+          <t>27059</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46595</t>
+          <t>47332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -7661,72 +7661,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3193</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8205</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3351</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1197</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7460</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1216</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7835</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3193</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>714</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8449</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13241</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>243953</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>243953</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>243953</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>358</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>249073</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>249073</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>249073</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>243953</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>243953</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>243953</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,67 +8004,67 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42212</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>34951</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>49144</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>54,08%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>44,77%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>62,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>38982</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>31448</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>45858</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32018</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>46726</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>52,4%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>42,27%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>61,64%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>42212</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>34140</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>49033</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>54,08%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70311</t>
+          <t>70784</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91140</t>
+          <t>91807</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,22%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>31224</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>24870</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>38714</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,86%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>49,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>24725</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>18771</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>32202</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>18530</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>31331</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>33,23%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>25,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>43,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>31224</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>24256</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>39045</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>40,0%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46236</t>
+          <t>46101</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66283</t>
+          <t>66558</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,66%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4625</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1666</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9195</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11,78%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>9986</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>5867</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>15839</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>15567</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>13,42%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>21,29%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>4625</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1763</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>10148</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22202</t>
+          <t>22595</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -8343,107 +8343,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>705</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3764</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3522</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4180</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>195326</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>180504</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>211427</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>54,46%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>50,33%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>58,95%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>191871</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>175656</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>207277</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>176381</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>207509</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>54,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>49,44%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>58,34%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>195326</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>179935</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>209968</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>54,46%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>364597</t>
+          <t>366765</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>408245</t>
+          <t>407943</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>133731</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>118154</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>148493</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>37,29%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>32,94%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>41,4%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>128156</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>112328</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>143418</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>111494</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>143362</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>36,07%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>31,62%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>40,37%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>133731</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>119256</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>149030</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>37,29%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>240870</t>
+          <t>241330</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>283003</t>
+          <t>284137</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -8912,72 +8912,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>25731</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>18095</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>35023</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>30496</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>22816</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>40988</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>22255</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>40487</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>8,58%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>25731</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>18012</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>34353</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45085</t>
+          <t>45132</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>68805</t>
+          <t>69520</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -9025,72 +9025,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3864</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8833</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>4763</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>2162</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>9952</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1872</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>9716</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,34%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3864</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1377</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>8806</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14464</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>358652</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>358652</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>358652</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>508</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>355286</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>355286</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>355286</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>358652</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>358652</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>358652</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
